--- a/games/future_spinner/library/future_spinner_full_statistics.xlsx
+++ b/games/future_spinner/library/future_spinner_full_statistics.xlsx
@@ -85,31 +85,31 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>1.496</t>
-  </si>
-  <si>
-    <t>5.52</t>
-  </si>
-  <si>
-    <t>10.012</t>
-  </si>
-  <si>
-    <t>87.51</t>
-  </si>
-  <si>
-    <t>85.628</t>
-  </si>
-  <si>
-    <t>58.553</t>
-  </si>
-  <si>
-    <t>102.256</t>
-  </si>
-  <si>
-    <t>1737.678</t>
-  </si>
-  <si>
-    <t>22054.143</t>
+    <t>1.501</t>
+  </si>
+  <si>
+    <t>6.016</t>
+  </si>
+  <si>
+    <t>8.963</t>
+  </si>
+  <si>
+    <t>62.629</t>
+  </si>
+  <si>
+    <t>71.948</t>
+  </si>
+  <si>
+    <t>58.904</t>
+  </si>
+  <si>
+    <t>114.615</t>
+  </si>
+  <si>
+    <t>1703.053</t>
+  </si>
+  <si>
+    <t>46716.72</t>
   </si>
   <si>
     <t>100000.001</t>
@@ -172,13 +172,13 @@
     <t>{'symbol': 'scatter'}</t>
   </si>
   <si>
-    <t>16.096557805889148</t>
+    <t>15.706694151911536</t>
   </si>
   <si>
     <t>6478</t>
   </si>
   <si>
-    <t>95.07297920192711</t>
+    <t>97.57620875615943</t>
   </si>
 </sst>
 </file>
@@ -541,10 +541,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.496</v>
+        <v>1.501</v>
       </c>
       <c r="C2">
-        <v>0.0003270089365256252</v>
+        <v>0.0001405812654839212</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -567,10 +567,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>5.52</v>
+        <v>6.016</v>
       </c>
       <c r="C3">
-        <v>0.1097623389177903</v>
+        <v>0.09915264902707593</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
@@ -593,10 +593,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>10.012</v>
+        <v>8.962999999999999</v>
       </c>
       <c r="C4">
-        <v>0.1272137770572964</v>
+        <v>0.1398661705340271</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -619,10 +619,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>87.51000000000001</v>
+        <v>62.629</v>
       </c>
       <c r="C5">
-        <v>0.03864770427424709</v>
+        <v>0.05423291112935776</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -645,10 +645,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>85.628</v>
+        <v>71.94799999999999</v>
       </c>
       <c r="C6">
-        <v>0.08568193573618406</v>
+        <v>0.1009376958760442</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -671,10 +671,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>58.553</v>
+        <v>58.904</v>
       </c>
       <c r="C7">
-        <v>0.2421270111808186</v>
+        <v>0.2364316821474623</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -697,10 +697,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>102.256</v>
+        <v>114.615</v>
       </c>
       <c r="C8">
-        <v>0.2696212688504349</v>
+        <v>0.2442982649334291</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -723,10 +723,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>1737.678</v>
+        <v>1703.053</v>
       </c>
       <c r="C9">
-        <v>0.03509712775707251</v>
+        <v>0.03598196364583187</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -749,10 +749,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>22054.143</v>
+        <v>46716.72</v>
       </c>
       <c r="C10">
-        <v>0.005021827238826386</v>
+        <v>0.002458081389937359</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -934,7 +934,7 @@
         <v>100000.001</v>
       </c>
       <c r="C17">
-        <v>0.04999999969878099</v>
+        <v>0.04999999969885738</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -997,13 +997,13 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>913.17</v>
+        <v>859.47</v>
       </c>
       <c r="C23">
-        <v>392.12</v>
+        <v>360.4</v>
       </c>
       <c r="D23">
-        <v>319.51</v>
+        <v>305.18</v>
       </c>
       <c r="G23" t="s">
         <v>34</v>
@@ -1021,13 +1021,13 @@
         <v>34</v>
       </c>
       <c r="N23">
-        <v>221.3</v>
+        <v>192.1</v>
       </c>
       <c r="O23">
-        <v>78.7</v>
+        <v>72.8</v>
       </c>
       <c r="P23">
-        <v>202.3</v>
+        <v>180.8</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1035,13 +1035,13 @@
         <v>35</v>
       </c>
       <c r="B24">
-        <v>509.7</v>
+        <v>528.21</v>
       </c>
       <c r="C24">
-        <v>200.16</v>
+        <v>209.76</v>
       </c>
       <c r="D24">
-        <v>128.94</v>
+        <v>139.49</v>
       </c>
       <c r="G24" t="s">
         <v>35</v>
@@ -1059,13 +1059,13 @@
         <v>35</v>
       </c>
       <c r="N24">
-        <v>76.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O24">
-        <v>109.1</v>
+        <v>102.5</v>
       </c>
       <c r="P24">
-        <v>87.09999999999999</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -1073,13 +1073,13 @@
         <v>36</v>
       </c>
       <c r="B25">
-        <v>113.67</v>
+        <v>112.93</v>
       </c>
       <c r="C25">
-        <v>96.45</v>
+        <v>88.45</v>
       </c>
       <c r="D25">
-        <v>124.91</v>
+        <v>108.92</v>
       </c>
       <c r="G25" t="s">
         <v>36</v>
@@ -1097,13 +1097,13 @@
         <v>36</v>
       </c>
       <c r="N25">
-        <v>95.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O25">
-        <v>89.8</v>
+        <v>84.8</v>
       </c>
       <c r="P25">
-        <v>124.1</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -1111,13 +1111,13 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>94.12</v>
+        <v>92.28</v>
       </c>
       <c r="C26">
-        <v>61.17</v>
+        <v>62.03</v>
       </c>
       <c r="D26">
-        <v>82.08</v>
+        <v>82.45</v>
       </c>
       <c r="G26" t="s">
         <v>37</v>
@@ -1135,13 +1135,13 @@
         <v>37</v>
       </c>
       <c r="N26">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="O26">
-        <v>89.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="P26">
-        <v>103.7</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -1149,13 +1149,13 @@
         <v>38</v>
       </c>
       <c r="B27">
-        <v>55.04</v>
+        <v>54.07</v>
       </c>
       <c r="C27">
-        <v>46.52</v>
+        <v>41.24</v>
       </c>
       <c r="D27">
-        <v>66.53</v>
+        <v>67.12</v>
       </c>
       <c r="G27" t="s">
         <v>38</v>
@@ -1173,13 +1173,13 @@
         <v>38</v>
       </c>
       <c r="N27">
-        <v>103.3</v>
+        <v>103</v>
       </c>
       <c r="O27">
-        <v>71.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="P27">
-        <v>74.3</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -1187,13 +1187,13 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>20.98</v>
+        <v>19.69</v>
       </c>
       <c r="C28">
-        <v>21.37</v>
+        <v>22.27</v>
       </c>
       <c r="D28">
-        <v>24.11</v>
+        <v>23.55</v>
       </c>
       <c r="G28" t="s">
         <v>39</v>
@@ -1211,13 +1211,13 @@
         <v>39</v>
       </c>
       <c r="N28">
-        <v>85</v>
+        <v>89.8</v>
       </c>
       <c r="O28">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P28">
-        <v>96.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -1225,13 +1225,13 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>27.63</v>
+        <v>25.4</v>
       </c>
       <c r="C29">
-        <v>42.15</v>
+        <v>35.86</v>
       </c>
       <c r="D29">
-        <v>70.26000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="G29" t="s">
         <v>40</v>
@@ -1249,13 +1249,13 @@
         <v>40</v>
       </c>
       <c r="N29">
-        <v>83.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="O29">
-        <v>105.5</v>
+        <v>104.7</v>
       </c>
       <c r="P29">
-        <v>136</v>
+        <v>126.1</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -1263,13 +1263,13 @@
         <v>41</v>
       </c>
       <c r="B30">
-        <v>19.18</v>
+        <v>19.03</v>
       </c>
       <c r="C30">
-        <v>24.58</v>
+        <v>27.16</v>
       </c>
       <c r="D30">
-        <v>64.94</v>
+        <v>65.56</v>
       </c>
       <c r="G30" t="s">
         <v>41</v>
@@ -1287,13 +1287,13 @@
         <v>41</v>
       </c>
       <c r="N30">
-        <v>84.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O30">
-        <v>101.4</v>
+        <v>104.7</v>
       </c>
       <c r="P30">
-        <v>98</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="35" spans="1:4">

--- a/games/future_spinner/library/future_spinner_full_statistics.xlsx
+++ b/games/future_spinner/library/future_spinner_full_statistics.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
+    <sheet name="bonus" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="87">
   <si>
     <t>Win Ranges</t>
   </si>
@@ -55,130 +56,226 @@
     <t>(200, 300)</t>
   </si>
   <si>
+    <t>(300, 500)</t>
+  </si>
+  <si>
+    <t>(500, 1000)</t>
+  </si>
+  <si>
+    <t>(1000, 2000)</t>
+  </si>
+  <si>
+    <t>(2000, 3000)</t>
+  </si>
+  <si>
+    <t>(3000, 5000)</t>
+  </si>
+  <si>
     <t>NaN</t>
   </si>
   <si>
-    <t>(300, 500)</t>
-  </si>
-  <si>
-    <t>(500, 1000)</t>
-  </si>
-  <si>
-    <t>(1000, 2000)</t>
-  </si>
-  <si>
-    <t>(2000, 3000)</t>
-  </si>
-  <si>
-    <t>(3000, 5000)</t>
-  </si>
-  <si>
     <t>(5000, 10000)</t>
   </si>
   <si>
-    <t>scatter</t>
+    <t>freegame</t>
   </si>
   <si>
     <t>basegame</t>
   </si>
   <si>
+    <t>1.005</t>
+  </si>
+  <si>
+    <t>1.403</t>
+  </si>
+  <si>
+    <t>702054.333</t>
+  </si>
+  <si>
+    <t>3.891</t>
+  </si>
+  <si>
+    <t>243776.08</t>
+  </si>
+  <si>
+    <t>223.728</t>
+  </si>
+  <si>
+    <t>48536.549</t>
+  </si>
+  <si>
+    <t>153.75</t>
+  </si>
+  <si>
+    <t>16501.897</t>
+  </si>
+  <si>
+    <t>206.188</t>
+  </si>
+  <si>
+    <t>4079.116</t>
+  </si>
+  <si>
+    <t>134.336</t>
+  </si>
+  <si>
+    <t>720.969</t>
+  </si>
+  <si>
+    <t>163.82</t>
+  </si>
+  <si>
+    <t>333.769</t>
+  </si>
+  <si>
+    <t>1204.654</t>
+  </si>
+  <si>
+    <t>1574.292</t>
+  </si>
+  <si>
+    <t>9059.764</t>
+  </si>
+  <si>
+    <t>30704.752</t>
+  </si>
+  <si>
+    <t>61918.336</t>
+  </si>
+  <si>
+    <t>167939.501</t>
+  </si>
+  <si>
+    <t>4052044.519</t>
+  </si>
+  <si>
+    <t>261347920.013</t>
+  </si>
+  <si>
+    <t>100000.001</t>
+  </si>
+  <si>
+    <t>HIT RATES</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SIM COUNTS</t>
+  </si>
+  <si>
+    <t>AVG WINS</t>
+  </si>
+  <si>
+    <t>CUSTOM</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>{'symbol': 'scatter'}</t>
+  </si>
+  <si>
+    <t>6.793727622373422</t>
+  </si>
+  <si>
+    <t>15200</t>
+  </si>
+  <si>
+    <t>96.40617041461078</t>
+  </si>
+  <si>
+    <t>2031.092</t>
+  </si>
+  <si>
+    <t>593.373</t>
+  </si>
+  <si>
+    <t>202.158</t>
+  </si>
+  <si>
+    <t>41.338</t>
+  </si>
+  <si>
+    <t>18.158</t>
+  </si>
+  <si>
+    <t>6.611</t>
+  </si>
+  <si>
+    <t>2.089</t>
+  </si>
+  <si>
+    <t>18.431</t>
+  </si>
+  <si>
+    <t>11.412</t>
+  </si>
+  <si>
+    <t>16.197</t>
+  </si>
+  <si>
+    <t>17.63</t>
+  </si>
+  <si>
+    <t>47.007</t>
+  </si>
+  <si>
+    <t>910.956</t>
+  </si>
+  <si>
+    <t>36547.559</t>
+  </si>
+  <si>
+    <t>842276.652</t>
+  </si>
+  <si>
+    <t>1000.0</t>
+  </si>
+  <si>
     <t>1.0</t>
   </si>
   <si>
-    <t>1.501</t>
-  </si>
-  <si>
-    <t>6.016</t>
-  </si>
-  <si>
-    <t>8.963</t>
-  </si>
-  <si>
-    <t>62.629</t>
-  </si>
-  <si>
-    <t>71.948</t>
-  </si>
-  <si>
-    <t>58.904</t>
-  </si>
-  <si>
-    <t>114.615</t>
-  </si>
-  <si>
-    <t>1703.053</t>
-  </si>
-  <si>
-    <t>46716.72</t>
-  </si>
-  <si>
-    <t>100000.001</t>
-  </si>
-  <si>
-    <t>HIT RATES</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>SIM COUNTS</t>
-  </si>
-  <si>
-    <t>AVG WINS</t>
-  </si>
-  <si>
-    <t>CUSTOM</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>COUNT</t>
-  </si>
-  <si>
-    <t>AVG</t>
-  </si>
-  <si>
-    <t>{'symbol': 'scatter'}</t>
-  </si>
-  <si>
-    <t>15.706694151911536</t>
-  </si>
-  <si>
-    <t>6478</t>
-  </si>
-  <si>
-    <t>97.57620875615943</t>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>9634.999999619702</t>
   </si>
 </sst>
 </file>
@@ -533,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="L1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -541,10 +638,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.501</v>
+        <v>1.403</v>
       </c>
       <c r="C2">
-        <v>0.0001405812654839212</v>
+        <v>0.0003040284394744263</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -559,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>40618</v>
+        <v>49853</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -567,25 +664,25 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>6.016</v>
+        <v>3.891</v>
       </c>
       <c r="C3">
-        <v>0.09915264902707593</v>
+        <v>0.1430152343511241</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
         <v>4</v>
       </c>
       <c r="L3">
-        <v>18942</v>
+        <v>12502</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -593,25 +690,25 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>8.962999999999999</v>
+        <v>451.301</v>
       </c>
       <c r="C4">
-        <v>0.1398661705340271</v>
+        <v>0.003286497912304126</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>11499</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -619,25 +716,25 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>62.629</v>
+        <v>215.88</v>
       </c>
       <c r="C5">
-        <v>0.05423291112935776</v>
+        <v>0.01566139151072199</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>14913</v>
+        <v>8386</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -645,25 +742,25 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>71.94799999999999</v>
+        <v>241.624</v>
       </c>
       <c r="C6">
-        <v>0.1009376958760442</v>
+        <v>0.03053635838192322</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
         <v>7</v>
       </c>
       <c r="L6">
-        <v>8165</v>
+        <v>4978</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -671,25 +768,25 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>58.904</v>
+        <v>139.187</v>
       </c>
       <c r="C7">
-        <v>0.2364316821474623</v>
+        <v>0.1047479232327124</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K7" t="s">
         <v>8</v>
       </c>
       <c r="L7">
-        <v>4357</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -697,25 +794,25 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>114.615</v>
+        <v>138.297</v>
       </c>
       <c r="C8">
-        <v>0.2442982649334291</v>
+        <v>0.2154815272735833</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K8" t="s">
         <v>9</v>
       </c>
       <c r="L8">
-        <v>1296</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -723,25 +820,25 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>1703.053</v>
+        <v>250.579</v>
       </c>
       <c r="C9">
-        <v>0.03598196364583187</v>
+        <v>0.2760364789895134</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>99</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -749,178 +846,178 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>46716.72</v>
+        <v>1175.624</v>
       </c>
       <c r="C10">
-        <v>0.002458081389937359</v>
+        <v>0.105258709974557</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K10" t="s">
         <v>11</v>
       </c>
       <c r="L10">
-        <v>11</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
+      <c r="B11">
+        <v>27892.654</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.008530590478247417</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
         <v>12</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
         <v>13</v>
       </c>
+      <c r="B12">
+        <v>59755.488</v>
+      </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.006284192447401043</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
         <v>13</v>
       </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
       <c r="L12">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>160934.034</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.004025363327723479</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>3702760.597</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.0003236725338730819</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>261347920.013</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>8.030176784621079E-06</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
         <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
         <v>18</v>
       </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -934,396 +1031,1168 @@
         <v>100000.001</v>
       </c>
       <c r="C17">
-        <v>0.04999999969885738</v>
+        <v>0.05004857869713028</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
         <v>19</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="M21" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I22" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J22" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="N22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="O22" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="P22" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B23">
-        <v>859.47</v>
+        <v>244.73</v>
       </c>
       <c r="C23">
-        <v>360.4</v>
+        <v>133.42</v>
       </c>
       <c r="D23">
-        <v>305.18</v>
+        <v>147.84</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H23">
-        <v>141</v>
+        <v>391</v>
       </c>
       <c r="I23">
-        <v>297</v>
+        <v>787</v>
       </c>
       <c r="J23">
-        <v>289</v>
+        <v>750</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="N23">
-        <v>192.1</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O23">
-        <v>72.8</v>
+        <v>94.2</v>
       </c>
       <c r="P23">
-        <v>180.8</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B24">
-        <v>528.21</v>
+        <v>172.81</v>
       </c>
       <c r="C24">
-        <v>209.76</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D24">
-        <v>139.49</v>
+        <v>54.49</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H24">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="I24">
-        <v>539</v>
+        <v>1468</v>
       </c>
       <c r="J24">
-        <v>708</v>
+        <v>1846</v>
       </c>
       <c r="M24" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="N24">
-        <v>77.09999999999999</v>
+        <v>107.7</v>
       </c>
       <c r="O24">
-        <v>102.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P24">
-        <v>89.7</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B25">
-        <v>112.93</v>
+        <v>46.77</v>
       </c>
       <c r="C25">
-        <v>88.45</v>
+        <v>31.43</v>
       </c>
       <c r="D25">
-        <v>108.92</v>
+        <v>46.93</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H25">
-        <v>885</v>
+        <v>2279</v>
       </c>
       <c r="I25">
-        <v>1137</v>
+        <v>2993</v>
       </c>
       <c r="J25">
-        <v>786</v>
+        <v>2056</v>
       </c>
       <c r="M25" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N25">
-        <v>92.90000000000001</v>
+        <v>104.1</v>
       </c>
       <c r="O25">
-        <v>84.8</v>
+        <v>82.3</v>
       </c>
       <c r="P25">
-        <v>112</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B26">
-        <v>92.28</v>
+        <v>32.19</v>
       </c>
       <c r="C26">
-        <v>62.03</v>
+        <v>24.4</v>
       </c>
       <c r="D26">
-        <v>82.45</v>
+        <v>30.91</v>
       </c>
       <c r="G26" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H26">
-        <v>1196</v>
+        <v>3202</v>
       </c>
       <c r="I26">
-        <v>1682</v>
+        <v>4336</v>
       </c>
       <c r="J26">
-        <v>1253</v>
+        <v>3318</v>
       </c>
       <c r="M26" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="N26">
-        <v>77.5</v>
+        <v>92.2</v>
       </c>
       <c r="O26">
-        <v>88</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P26">
-        <v>104.4</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B27">
-        <v>54.07</v>
+        <v>19.23</v>
       </c>
       <c r="C27">
-        <v>41.24</v>
+        <v>18.79</v>
       </c>
       <c r="D27">
-        <v>67.12</v>
+        <v>27.86</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H27">
-        <v>1884</v>
+        <v>5032</v>
       </c>
       <c r="I27">
-        <v>2087</v>
+        <v>5389</v>
       </c>
       <c r="J27">
-        <v>1414</v>
+        <v>3609</v>
       </c>
       <c r="M27" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="N27">
-        <v>103</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O27">
-        <v>74.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="P27">
-        <v>76.5</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B28">
-        <v>19.69</v>
+        <v>9.1</v>
       </c>
       <c r="C28">
-        <v>22.27</v>
+        <v>10.06</v>
       </c>
       <c r="D28">
-        <v>23.55</v>
+        <v>10.59</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H28">
-        <v>4573</v>
+        <v>11549</v>
       </c>
       <c r="I28">
-        <v>4324</v>
+        <v>10664</v>
       </c>
       <c r="J28">
-        <v>4405</v>
+        <v>9926</v>
       </c>
       <c r="M28" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="N28">
-        <v>89.8</v>
+        <v>89.5</v>
       </c>
       <c r="O28">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B29">
-        <v>25.4</v>
+        <v>11.06</v>
       </c>
       <c r="C29">
-        <v>35.86</v>
+        <v>17.13</v>
       </c>
       <c r="D29">
-        <v>73.31</v>
+        <v>29.54</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H29">
-        <v>3562</v>
+        <v>9363</v>
       </c>
       <c r="I29">
-        <v>2401</v>
+        <v>5823</v>
       </c>
       <c r="J29">
-        <v>1403</v>
+        <v>3554</v>
       </c>
       <c r="M29" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="N29">
-        <v>85.2</v>
+        <v>91.8</v>
       </c>
       <c r="O29">
-        <v>104.7</v>
+        <v>94.7</v>
       </c>
       <c r="P29">
-        <v>126.1</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B30">
-        <v>19.03</v>
+        <v>7.72</v>
       </c>
       <c r="C30">
-        <v>27.16</v>
+        <v>12.09</v>
       </c>
       <c r="D30">
-        <v>65.56</v>
+        <v>25.19</v>
       </c>
       <c r="G30" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H30">
-        <v>4965</v>
+        <v>12843</v>
       </c>
       <c r="I30">
-        <v>3483</v>
+        <v>8643</v>
       </c>
       <c r="J30">
-        <v>1629</v>
+        <v>4175</v>
       </c>
       <c r="M30" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="N30">
-        <v>83.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="O30">
-        <v>104.7</v>
+        <v>104</v>
       </c>
       <c r="P30">
-        <v>96.8</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1092.51</v>
+      </c>
+      <c r="C4">
+        <v>1.549015555946811E-05</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>77.833</v>
+      </c>
+      <c r="C5">
+        <v>0.0004768672740200297</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>23.432</v>
+      </c>
+      <c r="C6">
+        <v>0.003317357575178956</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>8.102</v>
+      </c>
+      <c r="C7">
+        <v>0.01877221320335517</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>1.882</v>
+      </c>
+      <c r="C8">
+        <v>0.1815113275302229</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8">
+        <v>15282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>18.564</v>
+      </c>
+      <c r="C9">
+        <v>0.04030661428805964</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>24046</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>11.433</v>
+      </c>
+      <c r="C10">
+        <v>0.1296447432352606</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10">
+        <v>27029</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>15.798</v>
+      </c>
+      <c r="C11">
+        <v>0.1559556808290181</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>13190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>16.83</v>
+      </c>
+      <c r="C12">
+        <v>0.2258582592428137</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12">
+        <v>10426</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>44.572</v>
+      </c>
+      <c r="C13">
+        <v>0.1430655876087145</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>873.421</v>
+      </c>
+      <c r="C14">
+        <v>0.01386448530123181</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>34369.344</v>
+      </c>
+      <c r="C15">
+        <v>0.0006667082692770525</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>842276.652</v>
+      </c>
+      <c r="C16">
+        <v>4.466544894673344E-05</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>1000</v>
+      </c>
+      <c r="C17">
+        <v>0.05006196725032307</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" t="s">
+        <v>56</v>
+      </c>
+      <c r="P22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23">
+        <v>40.13</v>
+      </c>
+      <c r="C23">
+        <v>21.79</v>
+      </c>
+      <c r="D23">
+        <v>23.72</v>
+      </c>
+      <c r="G23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23">
+        <v>2433</v>
+      </c>
+      <c r="I23">
+        <v>4410</v>
+      </c>
+      <c r="J23">
+        <v>4229</v>
+      </c>
+      <c r="M23" t="s">
+        <v>47</v>
+      </c>
+      <c r="N23">
+        <v>9535.5</v>
+      </c>
+      <c r="O23">
+        <v>9323.799999999999</v>
+      </c>
+      <c r="P23">
+        <v>9548.299999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24">
+        <v>24.24</v>
+      </c>
+      <c r="C24">
+        <v>11.76</v>
+      </c>
+      <c r="D24">
+        <v>9.65</v>
+      </c>
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24">
+        <v>4031</v>
+      </c>
+      <c r="I24">
+        <v>8655</v>
+      </c>
+      <c r="J24">
+        <v>10449</v>
+      </c>
+      <c r="M24" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24">
+        <v>9338.799999999999</v>
+      </c>
+      <c r="O24">
+        <v>9641.6</v>
+      </c>
+      <c r="P24">
+        <v>9725.299999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25">
+        <v>7.86</v>
+      </c>
+      <c r="C25">
+        <v>6.17</v>
+      </c>
+      <c r="D25">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25">
+        <v>12464</v>
+      </c>
+      <c r="I25">
+        <v>16257</v>
+      </c>
+      <c r="J25">
+        <v>11461</v>
+      </c>
+      <c r="M25" t="s">
+        <v>49</v>
+      </c>
+      <c r="N25">
+        <v>9561.299999999999</v>
+      </c>
+      <c r="O25">
+        <v>9492.9</v>
+      </c>
+      <c r="P25">
+        <v>9737.700000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26">
+        <v>5.59</v>
+      </c>
+      <c r="C26">
+        <v>4.11</v>
+      </c>
+      <c r="D26">
+        <v>5.54</v>
+      </c>
+      <c r="G26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26">
+        <v>18239</v>
+      </c>
+      <c r="I26">
+        <v>23725</v>
+      </c>
+      <c r="J26">
+        <v>18414</v>
+      </c>
+      <c r="M26" t="s">
+        <v>50</v>
+      </c>
+      <c r="N26">
+        <v>9716.5</v>
+      </c>
+      <c r="O26">
+        <v>9450.5</v>
+      </c>
+      <c r="P26">
+        <v>9776</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
         <v>51</v>
       </c>
+      <c r="B27">
+        <v>3.49</v>
+      </c>
+      <c r="C27">
+        <v>3.3</v>
+      </c>
+      <c r="D27">
+        <v>5.09</v>
+      </c>
+      <c r="G27" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27">
+        <v>28835</v>
+      </c>
+      <c r="I27">
+        <v>29963</v>
+      </c>
+      <c r="J27">
+        <v>19800</v>
+      </c>
+      <c r="M27" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27">
+        <v>9785.799999999999</v>
+      </c>
+      <c r="O27">
+        <v>9541.5</v>
+      </c>
+      <c r="P27">
+        <v>9890.200000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28">
+        <v>1.53</v>
+      </c>
+      <c r="C28">
+        <v>1.73</v>
+      </c>
+      <c r="D28">
+        <v>1.99</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28">
+        <v>65398</v>
+      </c>
+      <c r="I28">
+        <v>58027</v>
+      </c>
+      <c r="J28">
+        <v>50359</v>
+      </c>
+      <c r="M28" t="s">
+        <v>52</v>
+      </c>
+      <c r="N28">
+        <v>9616.5</v>
+      </c>
+      <c r="O28">
+        <v>9668.1</v>
+      </c>
+      <c r="P28">
+        <v>9671.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29">
+        <v>1.84</v>
+      </c>
+      <c r="C29">
+        <v>3.1</v>
+      </c>
+      <c r="D29">
+        <v>5.19</v>
+      </c>
+      <c r="G29" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29">
+        <v>54410</v>
+      </c>
+      <c r="I29">
+        <v>32958</v>
+      </c>
+      <c r="J29">
+        <v>19479</v>
+      </c>
+      <c r="M29" t="s">
+        <v>53</v>
+      </c>
+      <c r="N29">
+        <v>9605.4</v>
+      </c>
+      <c r="O29">
+        <v>9788</v>
+      </c>
+      <c r="P29">
+        <v>9752.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30">
+        <v>1.35</v>
+      </c>
+      <c r="C30">
+        <v>2.02</v>
+      </c>
+      <c r="D30">
+        <v>4.21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30">
+        <v>73470</v>
+      </c>
+      <c r="I30">
+        <v>50055</v>
+      </c>
+      <c r="J30">
+        <v>23416</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30">
+        <v>9574.1</v>
+      </c>
+      <c r="O30">
+        <v>9760.5</v>
+      </c>
+      <c r="P30">
+        <v>9508</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/games/future_spinner/library/future_spinner_full_statistics.xlsx
+++ b/games/future_spinner/library/future_spinner_full_statistics.xlsx
@@ -7,15 +7,16 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="base" sheetId="1" r:id="rId1"/>
-    <sheet name="bonus" sheetId="2" r:id="rId2"/>
+    <sheet name="cruise" sheetId="1" r:id="rId1"/>
+    <sheet name="antelite" sheetId="2" r:id="rId2"/>
+    <sheet name="super" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="113">
   <si>
     <t>Win Ranges</t>
   </si>
@@ -68,12 +69,12 @@
     <t>(2000, 3000)</t>
   </si>
   <si>
+    <t>NaN</t>
+  </si>
+  <si>
     <t>(3000, 5000)</t>
   </si>
   <si>
-    <t>NaN</t>
-  </si>
-  <si>
     <t>(5000, 10000)</t>
   </si>
   <si>
@@ -83,76 +84,73 @@
     <t>basegame</t>
   </si>
   <si>
-    <t>1.005</t>
-  </si>
-  <si>
-    <t>1.403</t>
-  </si>
-  <si>
-    <t>702054.333</t>
-  </si>
-  <si>
-    <t>3.891</t>
-  </si>
-  <si>
-    <t>243776.08</t>
-  </si>
-  <si>
-    <t>223.728</t>
-  </si>
-  <si>
-    <t>48536.549</t>
-  </si>
-  <si>
-    <t>153.75</t>
-  </si>
-  <si>
-    <t>16501.897</t>
-  </si>
-  <si>
-    <t>206.188</t>
-  </si>
-  <si>
-    <t>4079.116</t>
-  </si>
-  <si>
-    <t>134.336</t>
-  </si>
-  <si>
-    <t>720.969</t>
-  </si>
-  <si>
-    <t>163.82</t>
-  </si>
-  <si>
-    <t>333.769</t>
-  </si>
-  <si>
-    <t>1204.654</t>
-  </si>
-  <si>
-    <t>1574.292</t>
-  </si>
-  <si>
-    <t>9059.764</t>
-  </si>
-  <si>
-    <t>30704.752</t>
-  </si>
-  <si>
-    <t>61918.336</t>
-  </si>
-  <si>
-    <t>167939.501</t>
-  </si>
-  <si>
-    <t>4052044.519</t>
-  </si>
-  <si>
-    <t>261347920.013</t>
-  </si>
-  <si>
-    <t>100000.001</t>
+    <t>1.004</t>
+  </si>
+  <si>
+    <t>1.766</t>
+  </si>
+  <si>
+    <t>267526.285</t>
+  </si>
+  <si>
+    <t>2.548</t>
+  </si>
+  <si>
+    <t>110225.096</t>
+  </si>
+  <si>
+    <t>174.601</t>
+  </si>
+  <si>
+    <t>23721.944</t>
+  </si>
+  <si>
+    <t>105.313</t>
+  </si>
+  <si>
+    <t>7406.434</t>
+  </si>
+  <si>
+    <t>119.459</t>
+  </si>
+  <si>
+    <t>2102.168</t>
+  </si>
+  <si>
+    <t>116.941</t>
+  </si>
+  <si>
+    <t>529.017</t>
+  </si>
+  <si>
+    <t>127.644</t>
+  </si>
+  <si>
+    <t>832.319</t>
+  </si>
+  <si>
+    <t>815.644</t>
+  </si>
+  <si>
+    <t>11453.718</t>
+  </si>
+  <si>
+    <t>6841.077</t>
+  </si>
+  <si>
+    <t>1372454.586</t>
+  </si>
+  <si>
+    <t>2203186.15</t>
+  </si>
+  <si>
+    <t>4899306.97</t>
+  </si>
+  <si>
+    <t>61202672.392</t>
+  </si>
+  <si>
+    <t>250000.002</t>
   </si>
   <si>
     <t>HIT RATES</t>
@@ -212,61 +210,142 @@
     <t>{'symbol': 'scatter'}</t>
   </si>
   <si>
-    <t>6.793727622373422</t>
-  </si>
-  <si>
-    <t>15200</t>
-  </si>
-  <si>
-    <t>96.40617041461078</t>
-  </si>
-  <si>
-    <t>2031.092</t>
-  </si>
-  <si>
-    <t>593.373</t>
-  </si>
-  <si>
-    <t>202.158</t>
-  </si>
-  <si>
-    <t>41.338</t>
-  </si>
-  <si>
-    <t>18.158</t>
-  </si>
-  <si>
-    <t>6.611</t>
-  </si>
-  <si>
-    <t>2.089</t>
-  </si>
-  <si>
-    <t>18.431</t>
-  </si>
-  <si>
-    <t>11.412</t>
-  </si>
-  <si>
-    <t>16.197</t>
-  </si>
-  <si>
-    <t>17.63</t>
-  </si>
-  <si>
-    <t>47.007</t>
-  </si>
-  <si>
-    <t>910.956</t>
-  </si>
-  <si>
-    <t>36547.559</t>
-  </si>
-  <si>
-    <t>842276.652</t>
-  </si>
-  <si>
-    <t>1000.0</t>
+    <t>16.803535588047083</t>
+  </si>
+  <si>
+    <t>6100</t>
+  </si>
+  <si>
+    <t>91.5867069697746</t>
+  </si>
+  <si>
+    <t>1.009</t>
+  </si>
+  <si>
+    <t>1.411</t>
+  </si>
+  <si>
+    <t>357005.288</t>
+  </si>
+  <si>
+    <t>3.79</t>
+  </si>
+  <si>
+    <t>145372.62</t>
+  </si>
+  <si>
+    <t>189.021</t>
+  </si>
+  <si>
+    <t>24490.344</t>
+  </si>
+  <si>
+    <t>140.75</t>
+  </si>
+  <si>
+    <t>9717.109</t>
+  </si>
+  <si>
+    <t>198.281</t>
+  </si>
+  <si>
+    <t>2857.609</t>
+  </si>
+  <si>
+    <t>201.635</t>
+  </si>
+  <si>
+    <t>538.782</t>
+  </si>
+  <si>
+    <t>238.633</t>
+  </si>
+  <si>
+    <t>262.102</t>
+  </si>
+  <si>
+    <t>1843.473</t>
+  </si>
+  <si>
+    <t>445.446</t>
+  </si>
+  <si>
+    <t>11556.263</t>
+  </si>
+  <si>
+    <t>4845.375</t>
+  </si>
+  <si>
+    <t>16360.166</t>
+  </si>
+  <si>
+    <t>130402.134</t>
+  </si>
+  <si>
+    <t>3337509.742</t>
+  </si>
+  <si>
+    <t>246751814.593</t>
+  </si>
+  <si>
+    <t>80000.0</t>
+  </si>
+  <si>
+    <t>4.116228702293183</t>
+  </si>
+  <si>
+    <t>24250</t>
+  </si>
+  <si>
+    <t>124.27131277414124</t>
+  </si>
+  <si>
+    <t>23055.081</t>
+  </si>
+  <si>
+    <t>14406.297</t>
+  </si>
+  <si>
+    <t>11237.986</t>
+  </si>
+  <si>
+    <t>1572.311</t>
+  </si>
+  <si>
+    <t>320.424</t>
+  </si>
+  <si>
+    <t>87.062</t>
+  </si>
+  <si>
+    <t>12.058</t>
+  </si>
+  <si>
+    <t>4.738</t>
+  </si>
+  <si>
+    <t>2.664</t>
+  </si>
+  <si>
+    <t>32.332</t>
+  </si>
+  <si>
+    <t>120.676</t>
+  </si>
+  <si>
+    <t>6.101</t>
+  </si>
+  <si>
+    <t>9.872</t>
+  </si>
+  <si>
+    <t>170.849</t>
+  </si>
+  <si>
+    <t>994.392</t>
+  </si>
+  <si>
+    <t>250.083</t>
   </si>
   <si>
     <t>1.0</t>
@@ -275,7 +354,7 @@
     <t>100000</t>
   </si>
   <si>
-    <t>9634.999999619702</t>
+    <t>38539.99999957371</t>
   </si>
 </sst>
 </file>
@@ -630,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="L1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -638,10 +717,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.403</v>
+        <v>1.766</v>
       </c>
       <c r="C2">
-        <v>0.0003040284394744263</v>
+        <v>0.0003878206997754359</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -656,7 +735,7 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>49853</v>
+        <v>48146</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -664,10 +743,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3.891</v>
+        <v>2.548</v>
       </c>
       <c r="C3">
-        <v>0.1430152343511241</v>
+        <v>0.219173169689876</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
@@ -682,7 +761,7 @@
         <v>4</v>
       </c>
       <c r="L3">
-        <v>12502</v>
+        <v>16352</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -690,10 +769,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>451.301</v>
+        <v>251.284</v>
       </c>
       <c r="C4">
-        <v>0.003286497912304126</v>
+        <v>0.005948405843248785</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -708,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>6168</v>
+        <v>8072</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -716,10 +795,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>215.88</v>
+        <v>122.2</v>
       </c>
       <c r="C5">
-        <v>0.01566139151072199</v>
+        <v>0.02701838512614553</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -734,7 +813,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>8386</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -742,10 +821,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>241.624</v>
+        <v>125.027</v>
       </c>
       <c r="C6">
-        <v>0.03053635838192322</v>
+        <v>0.05775307416068165</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -760,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>4978</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -768,10 +847,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>139.187</v>
+        <v>115.62</v>
       </c>
       <c r="C7">
-        <v>0.1047479232327124</v>
+        <v>0.1252697860215103</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -786,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>2928</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -794,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>138.297</v>
+        <v>103.343</v>
       </c>
       <c r="C8">
-        <v>0.2154815272735833</v>
+        <v>0.3073729023973291</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -812,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>3777</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -820,10 +899,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>250.579</v>
+        <v>383.956</v>
       </c>
       <c r="C9">
-        <v>0.2760364789895134</v>
+        <v>0.1703529748733559</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -838,7 +917,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>4275</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -846,10 +925,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1175.624</v>
+        <v>3919.637</v>
       </c>
       <c r="C10">
-        <v>0.105258709974557</v>
+        <v>0.02969561564228064</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -864,7 +943,7 @@
         <v>11</v>
       </c>
       <c r="L10">
-        <v>3857</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -872,10 +951,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>27892.654</v>
+        <v>1270334.098</v>
       </c>
       <c r="C11">
-        <v>0.008530590478247417</v>
+        <v>0.0001895533280318585</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -884,13 +963,13 @@
         <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
         <v>12</v>
       </c>
       <c r="L11">
-        <v>1546</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -898,10 +977,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>59755.488</v>
+        <v>2136855.335</v>
       </c>
       <c r="C12">
-        <v>0.006284192447401043</v>
+        <v>0.0001765729685158957</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -910,13 +989,13 @@
         <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
         <v>13</v>
       </c>
       <c r="L12">
-        <v>1031</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -924,10 +1003,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>160934.034</v>
+        <v>4741055.706</v>
       </c>
       <c r="C13">
-        <v>0.004025363327723479</v>
+        <v>0.0001392484298629716</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -936,13 +1015,13 @@
         <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
         <v>14</v>
       </c>
       <c r="L13">
-        <v>456</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -950,10 +1029,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>3702760.597</v>
+        <v>57265292.734</v>
       </c>
       <c r="C14">
-        <v>0.0003236725338730819</v>
+        <v>2.249040731136337E-05</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -962,62 +1041,62 @@
         <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
       </c>
       <c r="L14">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>261347920.013</v>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
       <c r="C15">
-        <v>8.030176784621079E-06</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
         <v>16</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
         <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
         <v>17</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
         <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" t="s">
-        <v>17</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1028,399 +1107,399 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>100000.001</v>
+        <v>250000.002</v>
       </c>
       <c r="C17">
-        <v>0.05004857869713028</v>
+        <v>0.02001871627908525</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
         <v>19</v>
       </c>
       <c r="L17">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" t="s">
         <v>58</v>
-      </c>
-      <c r="M21" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>56</v>
       </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
       <c r="H22" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" t="s">
         <v>55</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>56</v>
       </c>
-      <c r="J22" t="s">
-        <v>57</v>
-      </c>
       <c r="N22" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" t="s">
         <v>55</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>56</v>
-      </c>
-      <c r="P22" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>244.73</v>
+        <v>429.91</v>
       </c>
       <c r="C23">
-        <v>133.42</v>
+        <v>229.13</v>
       </c>
       <c r="D23">
-        <v>147.84</v>
+        <v>220.3</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>391</v>
+        <v>220</v>
       </c>
       <c r="I23">
-        <v>787</v>
+        <v>433</v>
       </c>
       <c r="J23">
-        <v>750</v>
+        <v>467</v>
       </c>
       <c r="M23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N23">
-        <v>71.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O23">
-        <v>94.2</v>
+        <v>80.8</v>
       </c>
       <c r="P23">
-        <v>117.6</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24">
-        <v>172.81</v>
+        <v>278.37</v>
       </c>
       <c r="C24">
-        <v>67.09999999999999</v>
+        <v>85.09</v>
       </c>
       <c r="D24">
-        <v>54.49</v>
+        <v>88.62</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24">
-        <v>653</v>
+        <v>374</v>
       </c>
       <c r="I24">
-        <v>1468</v>
+        <v>855</v>
       </c>
       <c r="J24">
-        <v>1846</v>
+        <v>1140</v>
       </c>
       <c r="M24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24">
-        <v>107.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O24">
-        <v>96.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="P24">
-        <v>110.9</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25">
-        <v>46.77</v>
+        <v>76.28</v>
       </c>
       <c r="C25">
-        <v>31.43</v>
+        <v>45.03</v>
       </c>
       <c r="D25">
-        <v>46.93</v>
+        <v>63.48</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H25">
-        <v>2279</v>
+        <v>1389</v>
       </c>
       <c r="I25">
-        <v>2993</v>
+        <v>1817</v>
       </c>
       <c r="J25">
-        <v>2056</v>
+        <v>1310</v>
       </c>
       <c r="M25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25">
-        <v>104.1</v>
+        <v>103.4</v>
       </c>
       <c r="O25">
-        <v>82.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="P25">
-        <v>84.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26">
-        <v>32.19</v>
+        <v>58.54</v>
       </c>
       <c r="C26">
-        <v>24.4</v>
+        <v>39.34</v>
       </c>
       <c r="D26">
-        <v>30.91</v>
+        <v>49.78</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26">
-        <v>3202</v>
+        <v>1982</v>
       </c>
       <c r="I26">
-        <v>4336</v>
+        <v>2682</v>
       </c>
       <c r="J26">
-        <v>3318</v>
+        <v>2062</v>
       </c>
       <c r="M26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N26">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="O26">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="P26">
-        <v>81.90000000000001</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27">
-        <v>19.23</v>
+        <v>32.42</v>
       </c>
       <c r="C27">
-        <v>18.79</v>
+        <v>28.7</v>
       </c>
       <c r="D27">
-        <v>27.86</v>
+        <v>44.05</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27">
-        <v>5032</v>
+        <v>3066</v>
       </c>
       <c r="I27">
-        <v>5389</v>
+        <v>3341</v>
       </c>
       <c r="J27">
-        <v>3609</v>
+        <v>2214</v>
       </c>
       <c r="M27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N27">
-        <v>90.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="O27">
-        <v>95.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="P27">
-        <v>87.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28">
-        <v>9.1</v>
+        <v>13.83</v>
       </c>
       <c r="C28">
-        <v>10.06</v>
+        <v>15.87</v>
       </c>
       <c r="D28">
-        <v>10.59</v>
+        <v>16.21</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H28">
-        <v>11549</v>
+        <v>7069</v>
       </c>
       <c r="I28">
-        <v>10664</v>
+        <v>6565</v>
       </c>
       <c r="J28">
-        <v>9926</v>
+        <v>6459</v>
       </c>
       <c r="M28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N28">
-        <v>89.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O28">
-        <v>101</v>
+        <v>92.5</v>
       </c>
       <c r="P28">
-        <v>98.09999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29">
-        <v>11.06</v>
+        <v>18.6</v>
       </c>
       <c r="C29">
-        <v>17.13</v>
+        <v>25.23</v>
       </c>
       <c r="D29">
-        <v>29.54</v>
+        <v>46.6</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29">
-        <v>9363</v>
+        <v>5558</v>
       </c>
       <c r="I29">
-        <v>5823</v>
+        <v>3649</v>
       </c>
       <c r="J29">
-        <v>3554</v>
+        <v>2228</v>
       </c>
       <c r="M29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N29">
-        <v>91.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O29">
-        <v>94.7</v>
+        <v>96.5</v>
       </c>
       <c r="P29">
-        <v>80.8</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30">
-        <v>7.72</v>
+        <v>12.94</v>
       </c>
       <c r="C30">
-        <v>12.09</v>
+        <v>19.79</v>
       </c>
       <c r="D30">
-        <v>25.19</v>
+        <v>41.86</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H30">
-        <v>12843</v>
+        <v>7664</v>
       </c>
       <c r="I30">
-        <v>8643</v>
+        <v>5194</v>
       </c>
       <c r="J30">
-        <v>4175</v>
+        <v>2554</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N30">
-        <v>91.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="O30">
-        <v>104</v>
+        <v>115.8</v>
       </c>
       <c r="P30">
-        <v>110.6</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" t="s">
         <v>61</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s">
         <v>64</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>65</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>66</v>
-      </c>
-      <c r="D37" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1433,6 +1512,829 @@
   <dimension ref="A1:P37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1.411</v>
+      </c>
+      <c r="C2">
+        <v>0.0002145489065079868</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>42948</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>3.79</v>
+      </c>
+      <c r="C3">
+        <v>0.09038840079519803</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>11769</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>523.551</v>
+      </c>
+      <c r="C4">
+        <v>0.002240409080601431</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>5777</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>247.962</v>
+      </c>
+      <c r="C5">
+        <v>0.01092898707086321</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>7881</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>261.27</v>
+      </c>
+      <c r="C6">
+        <v>0.02282485331383504</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>223.604</v>
+      </c>
+      <c r="C7">
+        <v>0.05216884564731054</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>175.081</v>
+      </c>
+      <c r="C8">
+        <v>0.1436442842266638</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>5567</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>229.064</v>
+      </c>
+      <c r="C9">
+        <v>0.2571724092422011</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>6862</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>387.246</v>
+      </c>
+      <c r="C10">
+        <v>0.2672804483863142</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10">
+        <v>6251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>4373.755</v>
+      </c>
+      <c r="C11">
+        <v>0.04339839012750207</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>15191.903</v>
+      </c>
+      <c r="C12">
+        <v>0.01889882645131406</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>122911.147</v>
+      </c>
+      <c r="C13">
+        <v>0.004031175048223779</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>3166108.277</v>
+      </c>
+      <c r="C14">
+        <v>0.0003014664661787511</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>246751814.593</v>
+      </c>
+      <c r="C15">
+        <v>6.954043465051858E-06</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>80000</v>
+      </c>
+      <c r="C17">
+        <v>0.05005183009873576</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" t="s">
+        <v>55</v>
+      </c>
+      <c r="P22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23">
+        <v>157.2</v>
+      </c>
+      <c r="C23">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="D23">
+        <v>102.08</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23">
+        <v>597</v>
+      </c>
+      <c r="I23">
+        <v>1120</v>
+      </c>
+      <c r="J23">
+        <v>1077</v>
+      </c>
+      <c r="M23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23">
+        <v>95</v>
+      </c>
+      <c r="O23">
+        <v>113.3</v>
+      </c>
+      <c r="P23">
+        <v>136.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>97.27</v>
+      </c>
+      <c r="C24">
+        <v>47.6</v>
+      </c>
+      <c r="D24">
+        <v>40.54</v>
+      </c>
+      <c r="G24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24">
+        <v>1001</v>
+      </c>
+      <c r="I24">
+        <v>2173</v>
+      </c>
+      <c r="J24">
+        <v>2625</v>
+      </c>
+      <c r="M24" t="s">
+        <v>47</v>
+      </c>
+      <c r="N24">
+        <v>115.4</v>
+      </c>
+      <c r="O24">
+        <v>129.2</v>
+      </c>
+      <c r="P24">
+        <v>141.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>31</v>
+      </c>
+      <c r="C25">
+        <v>23.18</v>
+      </c>
+      <c r="D25">
+        <v>28.92</v>
+      </c>
+      <c r="G25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25">
+        <v>3286</v>
+      </c>
+      <c r="I25">
+        <v>4251</v>
+      </c>
+      <c r="J25">
+        <v>2972</v>
+      </c>
+      <c r="M25" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25">
+        <v>118.4</v>
+      </c>
+      <c r="O25">
+        <v>108.2</v>
+      </c>
+      <c r="P25">
+        <v>109.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>20.11</v>
+      </c>
+      <c r="C26">
+        <v>16.33</v>
+      </c>
+      <c r="D26">
+        <v>20.7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26">
+        <v>4703</v>
+      </c>
+      <c r="I26">
+        <v>6188</v>
+      </c>
+      <c r="J26">
+        <v>4778</v>
+      </c>
+      <c r="M26" t="s">
+        <v>49</v>
+      </c>
+      <c r="N26">
+        <v>115.4</v>
+      </c>
+      <c r="O26">
+        <v>114.9</v>
+      </c>
+      <c r="P26">
+        <v>116.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>13.21</v>
+      </c>
+      <c r="C27">
+        <v>13.03</v>
+      </c>
+      <c r="D27">
+        <v>17.95</v>
+      </c>
+      <c r="G27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27">
+        <v>7329</v>
+      </c>
+      <c r="I27">
+        <v>7737</v>
+      </c>
+      <c r="J27">
+        <v>5150</v>
+      </c>
+      <c r="M27" t="s">
+        <v>50</v>
+      </c>
+      <c r="N27">
+        <v>111.1</v>
+      </c>
+      <c r="O27">
+        <v>125.5</v>
+      </c>
+      <c r="P27">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>6.18</v>
+      </c>
+      <c r="C28">
+        <v>6.7</v>
+      </c>
+      <c r="D28">
+        <v>7.33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28">
+        <v>16727</v>
+      </c>
+      <c r="I28">
+        <v>15334</v>
+      </c>
+      <c r="J28">
+        <v>13989</v>
+      </c>
+      <c r="M28" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28">
+        <v>125.8</v>
+      </c>
+      <c r="O28">
+        <v>128.6</v>
+      </c>
+      <c r="P28">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>7.28</v>
+      </c>
+      <c r="C29">
+        <v>11.63</v>
+      </c>
+      <c r="D29">
+        <v>21.49</v>
+      </c>
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29">
+        <v>13686</v>
+      </c>
+      <c r="I29">
+        <v>8432</v>
+      </c>
+      <c r="J29">
+        <v>5116</v>
+      </c>
+      <c r="M29" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29">
+        <v>116.4</v>
+      </c>
+      <c r="O29">
+        <v>119.5</v>
+      </c>
+      <c r="P29">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30">
+        <v>5.25</v>
+      </c>
+      <c r="C30">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D30">
+        <v>16.79</v>
+      </c>
+      <c r="G30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30">
+        <v>18644</v>
+      </c>
+      <c r="I30">
+        <v>12467</v>
+      </c>
+      <c r="J30">
+        <v>6083</v>
+      </c>
+      <c r="M30" t="s">
+        <v>53</v>
+      </c>
+      <c r="N30">
+        <v>120.4</v>
+      </c>
+      <c r="O30">
+        <v>124.7</v>
+      </c>
+      <c r="P30">
+        <v>123.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
@@ -1450,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="K1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1458,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1467,7 +2369,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
         <v>3</v>
@@ -1481,7 +2383,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1490,7 +2392,7 @@
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
@@ -1503,23 +2405,23 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>1092.51</v>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>1.549015555946811E-05</v>
+        <v>0</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J4" t="s">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1527,22 +2429,22 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>77.833</v>
+        <v>3755.481</v>
       </c>
       <c r="C5">
-        <v>0.0004768672740200297</v>
+        <v>2.152973182438588E-06</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="J5" t="s">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>154</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1550,22 +2452,22 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>23.432</v>
+        <v>571.458</v>
       </c>
       <c r="C6">
-        <v>0.003317357575178956</v>
+        <v>3.470768457404665E-05</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="J6" t="s">
         <v>7</v>
       </c>
       <c r="K6">
-        <v>691</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1573,22 +2475,22 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>8.102</v>
+        <v>105.694</v>
       </c>
       <c r="C7">
-        <v>0.01877221320335517</v>
+        <v>0.0003712799839717648</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="J7" t="s">
         <v>8</v>
       </c>
       <c r="K7">
-        <v>2993</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1596,22 +2498,22 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>1.882</v>
+        <v>14.032</v>
       </c>
       <c r="C8">
-        <v>0.1815113275302229</v>
+        <v>0.006671157316472162</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="J8" t="s">
         <v>9</v>
       </c>
       <c r="K8">
-        <v>15282</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1619,22 +2521,22 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>18.564</v>
+        <v>4.806</v>
       </c>
       <c r="C9">
-        <v>0.04030661428805964</v>
+        <v>0.03859967739695968</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="J9" t="s">
         <v>10</v>
       </c>
       <c r="K9">
-        <v>24046</v>
+        <v>12208</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1642,22 +2544,22 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>11.433</v>
+        <v>2.571</v>
       </c>
       <c r="C10">
-        <v>0.1296447432352606</v>
+        <v>0.1334912164211547</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="J10" t="s">
         <v>11</v>
       </c>
       <c r="K10">
-        <v>27029</v>
+        <v>26066</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1665,22 +2567,22 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>15.798</v>
+        <v>27.968</v>
       </c>
       <c r="C11">
-        <v>0.1559556808290181</v>
+        <v>0.02017378645353706</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="J11" t="s">
         <v>12</v>
       </c>
       <c r="K11">
-        <v>13190</v>
+        <v>18343</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1688,22 +2590,22 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>16.83</v>
+        <v>125.364</v>
       </c>
       <c r="C12">
-        <v>0.2258582592428137</v>
+        <v>0.008418589876267576</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="J12" t="s">
         <v>13</v>
       </c>
       <c r="K12">
-        <v>10426</v>
+        <v>20216</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1711,22 +2613,22 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>44.572</v>
+        <v>6.206</v>
       </c>
       <c r="C13">
-        <v>0.1430655876087145</v>
+        <v>0.3345889893503866</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
       </c>
       <c r="K13">
-        <v>5060</v>
+        <v>13102</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1734,22 +2636,22 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>873.421</v>
+        <v>9.586</v>
       </c>
       <c r="C14">
-        <v>0.01386448530123181</v>
+        <v>0.3280718321708262</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>677</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1757,45 +2659,45 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>34369.344</v>
+        <v>167.36</v>
       </c>
       <c r="C15">
-        <v>0.0006667082692770525</v>
+        <v>0.03469810288291834</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="J15" t="s">
         <v>16</v>
       </c>
       <c r="K15">
-        <v>41</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>842276.652</v>
+        <v>995.712</v>
       </c>
       <c r="C16">
-        <v>4.466544894673344E-05</v>
+        <v>0.008378507497783785</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1803,396 +2705,396 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="C17">
-        <v>0.05006196725032307</v>
+        <v>0.05006349994794691</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
       </c>
       <c r="K17">
-        <v>400</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" t="s">
         <v>58</v>
-      </c>
-      <c r="M21" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>56</v>
       </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
       <c r="H22" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" t="s">
         <v>55</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>56</v>
       </c>
-      <c r="J22" t="s">
-        <v>57</v>
-      </c>
       <c r="N22" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" t="s">
         <v>55</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>56</v>
-      </c>
-      <c r="P22" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>40.13</v>
+        <v>38.54</v>
       </c>
       <c r="C23">
-        <v>21.79</v>
+        <v>22.16</v>
       </c>
       <c r="D23">
-        <v>23.72</v>
+        <v>24.59</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>2433</v>
+        <v>2390</v>
       </c>
       <c r="I23">
-        <v>4410</v>
+        <v>4320</v>
       </c>
       <c r="J23">
-        <v>4229</v>
+        <v>4133</v>
       </c>
       <c r="M23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N23">
-        <v>9535.5</v>
+        <v>34966</v>
       </c>
       <c r="O23">
-        <v>9323.799999999999</v>
+        <v>34784.5</v>
       </c>
       <c r="P23">
-        <v>9548.299999999999</v>
+        <v>38854.8</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24">
-        <v>24.24</v>
+        <v>24.63</v>
       </c>
       <c r="C24">
-        <v>11.76</v>
+        <v>11.7</v>
       </c>
       <c r="D24">
-        <v>9.65</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24">
-        <v>4031</v>
+        <v>3944</v>
       </c>
       <c r="I24">
-        <v>8655</v>
+        <v>8469</v>
       </c>
       <c r="J24">
-        <v>10449</v>
+        <v>10175</v>
       </c>
       <c r="M24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24">
-        <v>9338.799999999999</v>
+        <v>37564.8</v>
       </c>
       <c r="O24">
-        <v>9641.6</v>
+        <v>38016.3</v>
       </c>
       <c r="P24">
-        <v>9725.299999999999</v>
+        <v>36846.6</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25">
-        <v>7.86</v>
+        <v>8.27</v>
       </c>
       <c r="C25">
-        <v>6.17</v>
+        <v>6.45</v>
       </c>
       <c r="D25">
-        <v>8.609999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H25">
-        <v>12464</v>
+        <v>12144</v>
       </c>
       <c r="I25">
-        <v>16257</v>
+        <v>15838</v>
       </c>
       <c r="J25">
-        <v>11461</v>
+        <v>11140</v>
       </c>
       <c r="M25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25">
-        <v>9561.299999999999</v>
+        <v>37524.1</v>
       </c>
       <c r="O25">
-        <v>9492.9</v>
+        <v>37941.8</v>
       </c>
       <c r="P25">
-        <v>9737.700000000001</v>
+        <v>38217.9</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26">
+        <v>5.69</v>
+      </c>
+      <c r="C26">
+        <v>4.34</v>
+      </c>
+      <c r="D26">
         <v>5.59</v>
       </c>
-      <c r="C26">
-        <v>4.11</v>
-      </c>
-      <c r="D26">
-        <v>5.54</v>
-      </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26">
-        <v>18239</v>
+        <v>17802</v>
       </c>
       <c r="I26">
-        <v>23725</v>
+        <v>23156</v>
       </c>
       <c r="J26">
-        <v>18414</v>
+        <v>17946</v>
       </c>
       <c r="M26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N26">
-        <v>9716.5</v>
+        <v>38590.6</v>
       </c>
       <c r="O26">
-        <v>9450.5</v>
+        <v>38644.3</v>
       </c>
       <c r="P26">
-        <v>9776</v>
+        <v>39546</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="C27">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="D27">
-        <v>5.09</v>
+        <v>5.21</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27">
-        <v>28835</v>
+        <v>28140</v>
       </c>
       <c r="I27">
-        <v>29963</v>
+        <v>29162</v>
       </c>
       <c r="J27">
-        <v>19800</v>
+        <v>19325</v>
       </c>
       <c r="M27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N27">
-        <v>9785.799999999999</v>
+        <v>39272.8</v>
       </c>
       <c r="O27">
-        <v>9541.5</v>
+        <v>38504.6</v>
       </c>
       <c r="P27">
-        <v>9890.200000000001</v>
+        <v>38724.5</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="C28">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="D28">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H28">
-        <v>65398</v>
+        <v>63841</v>
       </c>
       <c r="I28">
-        <v>58027</v>
+        <v>56658</v>
       </c>
       <c r="J28">
-        <v>50359</v>
+        <v>49059</v>
       </c>
       <c r="M28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N28">
-        <v>9616.5</v>
+        <v>38816.4</v>
       </c>
       <c r="O28">
-        <v>9668.1</v>
+        <v>38963.8</v>
       </c>
       <c r="P28">
-        <v>9671.1</v>
+        <v>38527.7</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="C29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="D29">
-        <v>5.19</v>
+        <v>5.27</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29">
-        <v>54410</v>
+        <v>53193</v>
       </c>
       <c r="I29">
-        <v>32958</v>
+        <v>32187</v>
       </c>
       <c r="J29">
-        <v>19479</v>
+        <v>18968</v>
       </c>
       <c r="M29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N29">
-        <v>9605.4</v>
+        <v>38258.4</v>
       </c>
       <c r="O29">
-        <v>9788</v>
+        <v>39032.3</v>
       </c>
       <c r="P29">
-        <v>9752.1</v>
+        <v>38590.9</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="C30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="D30">
-        <v>4.21</v>
+        <v>4.46</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H30">
-        <v>73470</v>
+        <v>71885</v>
       </c>
       <c r="I30">
-        <v>50055</v>
+        <v>49030</v>
       </c>
       <c r="J30">
-        <v>23416</v>
+        <v>22850</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N30">
-        <v>9574.1</v>
+        <v>38176</v>
       </c>
       <c r="O30">
-        <v>9760.5</v>
+        <v>38731.8</v>
       </c>
       <c r="P30">
-        <v>9508</v>
+        <v>38411.9</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" t="s">
         <v>61</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
